--- a/results/Int All Data 0.5/Rando_fi_explain.xlsx
+++ b/results/Int All Data 0.5/Rando_fi_explain.xlsx
@@ -1676,466 +1676,466 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.0009618793054714326</v>
+        <v>-0.001200190322462302</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0002251092715297631</v>
+        <v>-0.0002133732577445624</v>
       </c>
       <c r="D3" t="n">
-        <v>7.78600023942866e-05</v>
+        <v>0.0001807902760423019</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0003054699214245871</v>
+        <v>-0.0001308534261323968</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0001362451260603181</v>
+        <v>-9.364220890978216e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0001407138561086308</v>
+        <v>0.0004963241818456776</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0001026519498941214</v>
+        <v>-0.0001728066504264403</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0003335106634229001</v>
+        <v>-0.001280680111542787</v>
       </c>
       <c r="J3" t="n">
-        <v>2.378651489809425e-06</v>
+        <v>-0.0003353671322255946</v>
       </c>
       <c r="K3" t="n">
-        <v>9.869909846540122e-05</v>
+        <v>0.0002012060146579275</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0001751790275075837</v>
+        <v>0.0001813910441690136</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0004230536292574328</v>
+        <v>0.0001608088717183742</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.000508626231404803</v>
+        <v>-0.0002256180521208439</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0002943472207073051</v>
+        <v>-0.001493766580475324</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.001220734497963746</v>
+        <v>8.33655775034414e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.001219099741258667</v>
+        <v>0.002144950825184237</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.0002495847965383014</v>
+        <v>0.000652587505774248</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0002326903924130075</v>
+        <v>-0.0001359135977277337</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0001365099427680516</v>
+        <v>0.0001176321322932183</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0009621119295077097</v>
+        <v>0.0001996516916312874</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0002638910741773182</v>
+        <v>0.0001792768605832262</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0006779180823935961</v>
+        <v>-0.0006501714210793285</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0004360787972997937</v>
+        <v>0.0005698314351707367</v>
       </c>
       <c r="Y3" t="n">
-        <v>-8.665486021457558e-05</v>
+        <v>0.0001249095428352776</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.483393073779992e-05</v>
+        <v>-0.0004085875448128685</v>
       </c>
       <c r="AA3" t="n">
-        <v>-8.527000889315568e-05</v>
+        <v>-2.009181323562323e-06</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0002006889381950372</v>
+        <v>7.684817957207435e-05</v>
       </c>
       <c r="AC3" t="n">
-        <v>-3.617110281945999e-05</v>
+        <v>-0.001276251838450742</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.002003401201196812</v>
+        <v>0.001301796556826074</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.003676561541842159</v>
+        <v>0.005186417161516083</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.0002000264099340831</v>
+        <v>-0.0001642351134112641</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.0001215840753839192</v>
+        <v>0.0002348153285135057</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0.0006025500468784617</v>
+        <v>9.132304182790539e-05</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.0006498774118956285</v>
+        <v>0.0001085542940988782</v>
       </c>
       <c r="AJ3" t="n">
-        <v>7.081184391476425e-05</v>
+        <v>0.001625543594896182</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.003887990381247338</v>
+        <v>0.00609053075346562</v>
       </c>
       <c r="AL3" t="n">
-        <v>-6.906496267493954e-05</v>
+        <v>-0.000403930034547837</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.001084112036715414</v>
+        <v>0.0009711866370009537</v>
       </c>
       <c r="AN3" t="n">
-        <v>-0.0008347925687669733</v>
+        <v>-0.0007564995664984542</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.0002741444753489664</v>
+        <v>0.0009002039556873231</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.0003455171474977359</v>
+        <v>-0.0003115044125559041</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.0004896334302584293</v>
+        <v>0.0005568274081299907</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.00352364483360867</v>
+        <v>0.00183343137237207</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.0002629284094251705</v>
+        <v>-0.0002576552742654415</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.0002802831337209022</v>
+        <v>0.0005408808943887357</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.0006808835141789182</v>
+        <v>0.001348905462623634</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.0004024948554792784</v>
+        <v>1.12187743686043e-05</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0.0007256422899900594</v>
+        <v>4.193521922464582e-05</v>
       </c>
       <c r="AX3" t="n">
-        <v>-4.475966049882762e-06</v>
+        <v>-0.0003912066144736603</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0.0003390262390220378</v>
+        <v>-0.0008720041397785894</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0.000415886676221675</v>
+        <v>-0.0009378551503426324</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0.0005138795542775621</v>
+        <v>-0.0005783708757965899</v>
       </c>
       <c r="BB3" t="n">
-        <v>-0.001437684568889102</v>
+        <v>-0.000680905771319854</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.0001129665721681028</v>
+        <v>-0.0001253340329359065</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.0001404540580469859</v>
+        <v>0.000169387828696177</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.0008527519128629788</v>
+        <v>-0.0002311243248432327</v>
       </c>
       <c r="BF3" t="n">
-        <v>-7.00645141168299e-05</v>
+        <v>-0.0007636251395404791</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.0002096054474416376</v>
+        <v>0.000449889871097976</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.0001673065240891214</v>
+        <v>-0.0005481646581634236</v>
       </c>
       <c r="BI3" t="n">
-        <v>-0.001640214601669486</v>
+        <v>0.0007419066627257721</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.0004294102266663602</v>
+        <v>-0.0003788332709884224</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.0006346480223066753</v>
+        <v>-0.0005813873774278687</v>
       </c>
       <c r="BL3" t="n">
-        <v>6.90549592301858e-06</v>
+        <v>-0.0002436011938973514</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.0006845679490886225</v>
+        <v>-0.001025669738376003</v>
       </c>
       <c r="BN3" t="n">
-        <v>-0.001173489240058419</v>
+        <v>0.0003522878579530311</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.880283190458522e-05</v>
+        <v>0.0001045561292783092</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0.0004320450707755352</v>
+        <v>-0.0003568220457947346</v>
       </c>
       <c r="BQ3" t="n">
         <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.0007561802591605714</v>
+        <v>-0.0002663030046848491</v>
       </c>
       <c r="BS3" t="n">
-        <v>-0.001065689110702851</v>
+        <v>-1.214929511713668e-06</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.0004407346164842884</v>
+        <v>0.0001729287333793372</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.0004426639672271115</v>
+        <v>-0.0004326315984515283</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0.002190397550646407</v>
+        <v>0.0001853318284187477</v>
       </c>
       <c r="BW3" t="n">
-        <v>-5.345866420158882e-07</v>
+        <v>-9.606147934679844e-06</v>
       </c>
       <c r="BX3" t="n">
-        <v>5.467714778909949e-05</v>
+        <v>0.000515065540978541</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0.002367453645752621</v>
+        <v>-0.001847388283604521</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-0.001706539900639272</v>
+        <v>-0.0017949672376422</v>
       </c>
       <c r="CA3" t="n">
-        <v>-9.176928490390094e-05</v>
+        <v>-4.536204597826447e-05</v>
       </c>
       <c r="CB3" t="n">
-        <v>-7.672434380380455e-05</v>
+        <v>-0.0003323506224931494</v>
       </c>
       <c r="CC3" t="n">
-        <v>-0.00135306643804444</v>
+        <v>-3.254958666361275e-05</v>
       </c>
       <c r="CD3" t="n">
-        <v>-0.003075156006144936</v>
+        <v>-0.001195351492840964</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0.002263203168766037</v>
+        <v>-0.001290663333781908</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.0003311574001088746</v>
+        <v>-0.0001063984907744198</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.0002097220187618253</v>
+        <v>-0.0004858286565286918</v>
       </c>
       <c r="CH3" t="n">
-        <v>-0.000216048416400263</v>
+        <v>0.0004274409034829019</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.0005678364969722971</v>
+        <v>0.0003508478406572491</v>
       </c>
       <c r="CJ3" t="n">
         <v>0</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.0006965802197762239</v>
+        <v>-4.062367905152463e-05</v>
       </c>
       <c r="CL3" t="n">
-        <v>-0.0004234017113106281</v>
+        <v>-0.0005377071855266214</v>
       </c>
       <c r="CM3" t="n">
-        <v>-0.0004145809558246305</v>
+        <v>0.0001857671022912932</v>
       </c>
       <c r="CN3" t="n">
-        <v>-0.0001443777520523259</v>
+        <v>0.0002817206324680755</v>
       </c>
       <c r="CO3" t="n">
-        <v>-0.0003777065095126941</v>
+        <v>-0.0001681666126728354</v>
       </c>
       <c r="CP3" t="n">
-        <v>5.727622750058559e-05</v>
+        <v>6.195817757027823e-05</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0.001456072902975153</v>
+        <v>-0.000176089106626508</v>
       </c>
       <c r="CR3" t="n">
-        <v>-0.0007208254100981715</v>
+        <v>-0.0002748325585862976</v>
       </c>
       <c r="CS3" t="n">
-        <v>-0.002038654935710225</v>
+        <v>-6.018032681099794e-05</v>
       </c>
       <c r="CT3" t="n">
-        <v>5.4838973936654e-05</v>
+        <v>0.0002717117904127009</v>
       </c>
       <c r="CU3" t="n">
-        <v>7.097300460009559e-05</v>
+        <v>-8.872016190447529e-05</v>
       </c>
       <c r="CV3" t="n">
-        <v>5.084752226078851e-06</v>
+        <v>-2.929603965916238e-05</v>
       </c>
       <c r="CW3" t="n">
         <v>0</v>
       </c>
       <c r="CX3" t="n">
-        <v>-0.0006259252835418415</v>
+        <v>-0.0002841143348960007</v>
       </c>
       <c r="CY3" t="n">
-        <v>-2.648052413667945e-05</v>
+        <v>-0.0002935762292143508</v>
       </c>
       <c r="CZ3" t="n">
-        <v>4.724409448819022e-05</v>
+        <v>-0.0001277018076944903</v>
       </c>
       <c r="DA3" t="n">
-        <v>2.775225602839936e-05</v>
+        <v>0.0001002034085141134</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.0001801615663732192</v>
+        <v>5.091228236119294e-05</v>
       </c>
       <c r="DC3" t="n">
-        <v>-0.0001101566440426305</v>
+        <v>-0.0001233586697628408</v>
       </c>
       <c r="DD3" t="n">
-        <v>8.184486554612118e-06</v>
+        <v>-0.0001902079135365797</v>
       </c>
       <c r="DE3" t="n">
-        <v>-2.676171502572265e-05</v>
+        <v>-0.0004619753095571411</v>
       </c>
       <c r="DF3" t="n">
-        <v>-0.0001731042658285842</v>
+        <v>-0.001838018645665462</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.0001361458549620565</v>
+        <v>-5.648323943618248e-05</v>
       </c>
       <c r="DH3" t="n">
-        <v>-0.0005850791722224446</v>
+        <v>9.305964142522609e-05</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.0004493375159634307</v>
+        <v>-0.0003803260899741123</v>
       </c>
       <c r="DJ3" t="n">
-        <v>-0.0006018107915988101</v>
+        <v>-0.0001382276037150043</v>
       </c>
       <c r="DK3" t="n">
-        <v>-0.0001058926866960563</v>
+        <v>-0.0007190446362809255</v>
       </c>
       <c r="DL3" t="n">
-        <v>7.537166976610444e-05</v>
+        <v>6.688052083502204e-06</v>
       </c>
       <c r="DM3" t="n">
-        <v>-4.660333550733586e-05</v>
+        <v>-0.0004479591587364685</v>
       </c>
       <c r="DN3" t="n">
-        <v>-0.001083671198686587</v>
+        <v>-0.001981504040097631</v>
       </c>
       <c r="DO3" t="n">
-        <v>-7.285016592411319e-05</v>
+        <v>-9.828654862829907e-05</v>
       </c>
       <c r="DP3" t="n">
-        <v>-0.001311505600933611</v>
+        <v>-0.0001044483642018079</v>
       </c>
       <c r="DQ3" t="n">
-        <v>-4.124962661803954e-05</v>
+        <v>-2.239756781787449e-05</v>
       </c>
       <c r="DR3" t="n">
-        <v>-0.0001151150727086026</v>
+        <v>-3.878310695144993e-05</v>
       </c>
       <c r="DS3" t="n">
-        <v>-0.000111786538396792</v>
+        <v>0.0001684619206257065</v>
       </c>
       <c r="DT3" t="n">
-        <v>-0.0007744363289402244</v>
+        <v>-0.001364904442013778</v>
       </c>
       <c r="DU3" t="n">
-        <v>-0.001112579983624445</v>
+        <v>-0.00245108950199625</v>
       </c>
       <c r="DV3" t="n">
         <v>0</v>
       </c>
       <c r="DW3" t="n">
-        <v>-0.0001403805459037322</v>
+        <v>-0.0002045035161316455</v>
       </c>
       <c r="DX3" t="n">
-        <v>-0.0004320720675872558</v>
+        <v>-0.0003893512777625308</v>
       </c>
       <c r="DY3" t="n">
-        <v>-0.001682326782999226</v>
+        <v>0.0005763149521412725</v>
       </c>
       <c r="DZ3" t="n">
-        <v>2.253757591089589e-05</v>
+        <v>0.0002496896722638153</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0.001208898106053931</v>
+        <v>8.85336553619087e-05</v>
       </c>
       <c r="EB3" t="n">
-        <v>-0.0009229820490613683</v>
+        <v>-0.000439288446946976</v>
       </c>
       <c r="EC3" t="n">
-        <v>0.0001047475009214027</v>
+        <v>-0.000270828816972103</v>
       </c>
       <c r="ED3" t="n">
-        <v>0.0002130867255230384</v>
+        <v>3.815795108356155e-06</v>
       </c>
       <c r="EE3" t="n">
-        <v>-2.359603586597481e-05</v>
+        <v>0</v>
       </c>
       <c r="EF3" t="n">
-        <v>0.0002675404188804698</v>
+        <v>9.985779402655992e-05</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.0005330274373679266</v>
+        <v>0.0003126614316640486</v>
       </c>
       <c r="EH3" t="n">
-        <v>3.612086261757797e-05</v>
+        <v>5.646018078048766e-05</v>
       </c>
       <c r="EI3" t="n">
-        <v>-5.246800458192481e-05</v>
+        <v>-0.0003496702629871385</v>
       </c>
       <c r="EJ3" t="n">
-        <v>-0.0001715847241417934</v>
+        <v>-0.0005224526487208269</v>
       </c>
       <c r="EK3" t="n">
-        <v>-1.555611693461634e-05</v>
+        <v>-0.0006599259535154</v>
       </c>
       <c r="EL3" t="n">
-        <v>0</v>
+        <v>6.940854252913464e-05</v>
       </c>
       <c r="EM3" t="n">
-        <v>-0.0001404175722440304</v>
+        <v>8.449418568367339e-05</v>
       </c>
       <c r="EN3" t="n">
-        <v>-2.779331103419435e-05</v>
+        <v>-5.294488325352509e-06</v>
       </c>
       <c r="EO3" t="n">
         <v>0</v>
       </c>
       <c r="EP3" t="n">
-        <v>4.601932811780784e-06</v>
+        <v>5.719206187974057e-06</v>
       </c>
       <c r="EQ3" t="n">
-        <v>-0.0002830280283075415</v>
+        <v>-0.0002766167267854558</v>
       </c>
       <c r="ER3" t="n">
-        <v>5.249343832021136e-06</v>
+        <v>3.659472106696482e-05</v>
       </c>
       <c r="ES3" t="n">
-        <v>-1.328609388839497e-05</v>
+        <v>1.389427942604993e-05</v>
       </c>
       <c r="ET3" t="n">
-        <v>-0.0003573252990953069</v>
+        <v>-0.0001365497860020748</v>
       </c>
       <c r="EU3" t="n">
-        <v>-0.0001247721920745093</v>
+        <v>-0.0001028813078383228</v>
       </c>
       <c r="EV3" t="n">
-        <v>2.349652118800005e-05</v>
+        <v>1.619079110846688e-05</v>
       </c>
       <c r="EW3" t="n">
-        <v>-0.0003797985700652206</v>
+        <v>-0.0004790913866208802</v>
       </c>
       <c r="EX3" t="n">
-        <v>6.230757126648442e-06</v>
+        <v>-0.0001968625040173388</v>
       </c>
       <c r="EY3" t="n">
-        <v>-0.0002098371784428377</v>
+        <v>-0.000409875594737783</v>
       </c>
     </row>
     <row r="4">
@@ -2145,466 +2145,466 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0038080272105334</v>
+        <v>0.00168885922842364</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0007064179245076853</v>
+        <v>0.0008662752322933136</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0005368780825196095</v>
+        <v>0.001039081206789888</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0005061731076611218</v>
+        <v>0.0009329109134623773</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0003557198408721766</v>
+        <v>0.0009333075157336363</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00238790367493618</v>
+        <v>0.0009618433930939674</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001196258070544981</v>
+        <v>0.001559176844281864</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002316518257935937</v>
+        <v>0.001274801940443678</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002146581068321332</v>
+        <v>0.002332436252990947</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0005746350640972317</v>
+        <v>0.000327326083577217</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0006846620455688631</v>
+        <v>0.0003031736996946354</v>
       </c>
       <c r="M4" t="n">
-        <v>0.001816826102859732</v>
+        <v>0.001638932327927842</v>
       </c>
       <c r="N4" t="n">
-        <v>0.004301344803685632</v>
+        <v>0.003159524904034048</v>
       </c>
       <c r="O4" t="n">
-        <v>0.002702385396172473</v>
+        <v>0.002950580716045303</v>
       </c>
       <c r="P4" t="n">
-        <v>0.002290516782690874</v>
+        <v>0.001292959257682738</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.004118185602377287</v>
+        <v>0.005708017827302081</v>
       </c>
       <c r="R4" t="n">
-        <v>0.00179363138919067</v>
+        <v>0.0008908752861029315</v>
       </c>
       <c r="S4" t="n">
-        <v>0.00539110452847644</v>
+        <v>0.003250098120216012</v>
       </c>
       <c r="T4" t="n">
-        <v>0.001198732108571474</v>
+        <v>0.0004681491955465307</v>
       </c>
       <c r="U4" t="n">
-        <v>0.003302655247140185</v>
+        <v>0.0007367759362822241</v>
       </c>
       <c r="V4" t="n">
-        <v>0.002552270955080398</v>
+        <v>0.001406341051623672</v>
       </c>
       <c r="W4" t="n">
-        <v>0.001729099873548768</v>
+        <v>0.002321795156972011</v>
       </c>
       <c r="X4" t="n">
-        <v>0.003574283007303156</v>
+        <v>0.00150901142383864</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0003190452173916846</v>
+        <v>0.000325162924743375</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.001353882680810808</v>
+        <v>0.004627018948112915</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.003121807772924467</v>
+        <v>0.001615263843029096</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0006297234769481858</v>
+        <v>0.0004838460475449428</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.003551274734783109</v>
+        <v>0.001649115528342356</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.008635690855082194</v>
+        <v>0.006680356828796853</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.01010099045044783</v>
+        <v>0.01462430242857903</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.002110124116486019</v>
+        <v>0.002839255602700511</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.0006136666771766833</v>
+        <v>0.0005504806752031548</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.001653850810274142</v>
+        <v>0.0008973290219622667</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.001487147550383529</v>
+        <v>0.001112245679636145</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.002616832998318581</v>
+        <v>0.005340213059995499</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.0107226324309314</v>
+        <v>0.01309626154934364</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.0005846108429879597</v>
+        <v>0.001018654973901939</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.006771182414075297</v>
+        <v>0.005361741852434041</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.002325322403016724</v>
+        <v>0.001808569942557078</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.004173568021452135</v>
+        <v>0.00180940026547257</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.0007364347544552819</v>
+        <v>0.0005154552297822564</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.001156913873346928</v>
+        <v>0.001238766929717037</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.01479086171638544</v>
+        <v>0.01226049308789556</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.0009961814936228423</v>
+        <v>0.0009781340904764099</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.0008933456796790334</v>
+        <v>0.003046769591498865</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.001586020342257231</v>
+        <v>0.003005359269679096</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.001246387514640647</v>
+        <v>0.0006812380976661208</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.002905252404438695</v>
+        <v>0.00107617416818134</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.0003901684677952647</v>
+        <v>0.0009441730664518084</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.002407955815332465</v>
+        <v>0.002237678598028099</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.002785453261449044</v>
+        <v>0.002994948423181503</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.001370448766038722</v>
+        <v>0.002450188655625542</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.004985600367752561</v>
+        <v>0.002653065244900678</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.0006047604664663813</v>
+        <v>0.0008734079306073582</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.0004979709202281696</v>
+        <v>0.0003049315896997284</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.004421836897437058</v>
+        <v>0.00232881288239467</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.002971285094584465</v>
+        <v>0.002084727959346701</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.00215735206665967</v>
+        <v>0.001590255926328146</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.001579977388778419</v>
+        <v>0.00118558424887175</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.008034168890908288</v>
+        <v>0.005761285433938061</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.002342433768389516</v>
+        <v>0.001361504947421097</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.003399728707356806</v>
+        <v>0.002485608394674567</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.0003602803414306393</v>
+        <v>0.0004921257266857919</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.001135211967170662</v>
+        <v>0.001534622055874929</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.003846203406819904</v>
+        <v>0.003179859873973318</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.002224139211440965</v>
+        <v>0.001743532666166045</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.00101282327214279</v>
+        <v>0.0009212802415616507</v>
       </c>
       <c r="BQ4" t="n">
         <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.003593964240190577</v>
+        <v>0.001882548975904804</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.00215741094723196</v>
+        <v>0.0009861033948684729</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.0009024842314664307</v>
+        <v>0.0006820437944555196</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.001351094787397109</v>
+        <v>0.0007872999579889957</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.006517865823741019</v>
+        <v>0.001634972376502791</v>
       </c>
       <c r="BW4" t="n">
-        <v>2.351263672999463e-05</v>
+        <v>3.037730701411069e-05</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.0008090102200799703</v>
+        <v>0.000808241227357758</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.004357930628881282</v>
+        <v>0.005785540305720804</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.003608684916188512</v>
+        <v>0.006669504831958481</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.001236930844470503</v>
+        <v>0.001731917925006832</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.0006608309157253782</v>
+        <v>0.001054947261645329</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.004473166032798999</v>
+        <v>0.0008718709110130873</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.008483433187990707</v>
+        <v>0.001916838084921939</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.00541514683723487</v>
+        <v>0.001818551868707339</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.001685563383017054</v>
+        <v>0.0009988167582704848</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.00217209367114548</v>
+        <v>0.0007601008597893149</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.0009052797113347682</v>
+        <v>0.0005896489701119087</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.001130177987499412</v>
+        <v>0.001300621489073847</v>
       </c>
       <c r="CJ4" t="n">
         <v>0</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.0007173234734324753</v>
+        <v>0.00119766214523309</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.001093280122811315</v>
+        <v>0.001416782238874756</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.0008319303259172309</v>
+        <v>0.0006825109854893774</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.0004650616527759287</v>
+        <v>0.000611971809690856</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.001035750467192896</v>
+        <v>0.0006545790501638657</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.000117901942075276</v>
+        <v>0.0002233074755628245</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.003600041116947548</v>
+        <v>0.001160236321775826</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.002627589049136492</v>
+        <v>0.001604276936615073</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.002625722811940781</v>
+        <v>0.000491019282974184</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.002527954309206469</v>
+        <v>0.00126586529373439</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.000172958993995445</v>
+        <v>0.0004012904454546005</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.0001821864782676554</v>
+        <v>0.000252016490866745</v>
       </c>
       <c r="CW4" t="n">
         <v>0</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.002090873190149598</v>
+        <v>0.001174040295253378</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.00192880467920444</v>
+        <v>0.001417853018099541</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.000149398944574888</v>
+        <v>0.0002709251301609214</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.0004154627736469539</v>
+        <v>0.0004223940706629644</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.0009765430097494837</v>
+        <v>0.001030460942540545</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.00119455727703414</v>
+        <v>0.000933730235487303</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.0004510437572561149</v>
+        <v>0.0004175066907919046</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.0004389967614871032</v>
+        <v>0.001427757802597249</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.001575757589772869</v>
+        <v>0.005747395865825749</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.0009973254524744874</v>
+        <v>0.001101130090394832</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.002035662603158967</v>
+        <v>0.002595937142818121</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.002147782300273919</v>
+        <v>0.00216327195175686</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.002909277693299092</v>
+        <v>0.0008249113581603745</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.0005948119424262876</v>
+        <v>0.001913784867639177</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.0001647189186301416</v>
+        <v>0.0001291068172122091</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.0003241569907630674</v>
+        <v>0.001100327894382568</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.003394666699650175</v>
+        <v>0.004064003435014218</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.001477442349712008</v>
+        <v>0.001595657479012932</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.004167381640233617</v>
+        <v>0.001488194507315961</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.0002812041231043736</v>
+        <v>0.0002899494022331164</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.0002718603401106543</v>
+        <v>0.0001269248313052929</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.0003976996456656015</v>
+        <v>0.0002765443880089087</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.002551810398984826</v>
+        <v>0.00335712915557816</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.00137506358242985</v>
+        <v>0.003565284696796355</v>
       </c>
       <c r="DV4" t="n">
         <v>0</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.0002920433554259145</v>
+        <v>0.0005092354006095548</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.000816519483057446</v>
+        <v>0.0009102188297984498</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.00291767937158054</v>
+        <v>0.003922916375598265</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.000113990977712593</v>
+        <v>0.0006258607960769277</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.004487188047519932</v>
+        <v>0.0006358361351594126</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.001948697569413131</v>
+        <v>0.0009438258636611742</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.001426237547762658</v>
+        <v>0.001077411693279597</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.0008191473217083839</v>
+        <v>0.0008825571339670012</v>
       </c>
       <c r="EE4" t="n">
-        <v>7.461721708750397e-05</v>
+        <v>0</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.0006849738472985138</v>
+        <v>0.0003592670018615034</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.001135483931393261</v>
+        <v>0.0006906220735650565</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.0001124976695741603</v>
+        <v>0.0007174190938032673</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.001211118998266311</v>
+        <v>0.001058840394097109</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.0008944761511722963</v>
+        <v>0.002376984934445985</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.0005087346573741711</v>
+        <v>0.001298142771091702</v>
       </c>
       <c r="EL4" t="n">
-        <v>0</v>
+        <v>0.0002788798726315055</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.0003363547043076342</v>
+        <v>0.0003499818790468257</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.0001249059843149576</v>
+        <v>5.232322732348508e-05</v>
       </c>
       <c r="EO4" t="n">
         <v>0</v>
       </c>
       <c r="EP4" t="n">
-        <v>1.455258932429023e-05</v>
+        <v>3.770653611188363e-05</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.001585529144622951</v>
+        <v>0.0006431216708949666</v>
       </c>
       <c r="ER4" t="n">
-        <v>1.659988273054311e-05</v>
+        <v>8.546006481500694e-05</v>
       </c>
       <c r="ES4" t="n">
-        <v>4.201431789417104e-05</v>
+        <v>7.012306694047875e-05</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.0006419509706797753</v>
+        <v>0.0009022963325657229</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.0005458300567243772</v>
+        <v>0.001008318082251527</v>
       </c>
       <c r="EV4" t="n">
-        <v>5.071766978419203e-05</v>
+        <v>6.924887901998409e-05</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.001193803436698055</v>
+        <v>0.00284237711072808</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.0004188581778432021</v>
+        <v>0.0007105426661753</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.00104562748962852</v>
+        <v>0.0007399761110057523</v>
       </c>
     </row>
     <row r="5">
@@ -2614,466 +2614,466 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.009325210871602652</v>
+        <v>-0.004196133899104238</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.0008966493629070426</v>
+        <v>-0.001873198847262281</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0007550731477111938</v>
+        <v>-0.001651722510618236</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.001469816272965851</v>
+        <v>-0.00210871602624183</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0006824146981627366</v>
+        <v>-0.002296450939457184</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.002393005062126119</v>
+        <v>-0.0006134969325153449</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.002312411514865531</v>
+        <v>-0.003170028818443826</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.004761904761904712</v>
+        <v>-0.003308128544423494</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.002882797731569064</v>
+        <v>-0.006246719160104941</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.001049868766404172</v>
+        <v>-0.0002362948960302758</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0007966260543580295</v>
+        <v>-0.0001937984496124035</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.004573314474304535</v>
+        <v>-0.003441772748703464</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.008388003748828509</v>
+        <v>-0.00473289597000941</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.007638238050609203</v>
+        <v>-0.009231490159325229</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.006666666666666643</v>
+        <v>-0.002192066805845494</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.004639175257731987</v>
+        <v>-0.005511811023622038</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.003254593175852993</v>
+        <v>-0.0003308128544423861</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.009793814432989711</v>
+        <v>-0.005951265229615787</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.003464566929133839</v>
+        <v>-0.0007828810020876764</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.009816272965879258</v>
+        <v>-0.001043841336116902</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.004545454545454575</v>
+        <v>-0.002624671916010457</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.003280224929709496</v>
+        <v>-0.005998125585754499</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.007591377694470491</v>
+        <v>-0.001200768491834825</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.0007078810759792442</v>
+        <v>-0.0002828854314003149</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.002572178477690279</v>
+        <v>-0.01291338582677164</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.006841611996251195</v>
+        <v>-0.003682170542635665</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.0003780718336484079</v>
+        <v>-0.0007088846880907718</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.005388940955951271</v>
+        <v>-0.004860783388390788</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.01151486550259556</v>
+        <v>-0.01117397454031122</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.01700288184438038</v>
+        <v>-0.02012487992315086</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.004739990796134408</v>
+        <v>-0.005329457364341095</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.0004243281471003835</v>
+        <v>-0.0004199475065616798</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.004920337394564223</v>
+        <v>-0.00188976377952752</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.001417183348095619</v>
+        <v>-0.0008398950131233707</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.002737752161383267</v>
+        <v>-0.003650336215177774</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.01239981140971236</v>
+        <v>-0.01157540826128726</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.0009429514380009163</v>
+        <v>-0.002436738519212778</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.01455576559546319</v>
+        <v>-0.006082036775106126</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.005285512033978257</v>
+        <v>-0.00372817366682402</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.009418931583880064</v>
+        <v>-0.002641690682036557</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.0009438414346389923</v>
+        <v>-0.001008645533141261</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.002483598875351489</v>
+        <v>-0.001008645533141261</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.02365393465255413</v>
+        <v>-0.02363112391930837</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0.002079395085066216</v>
+        <v>-0.001565762004175353</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0.001043841336116902</v>
+        <v>-0.001968134957825685</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.001008645533141195</v>
+        <v>-0.0005154639175257936</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.0008034026465028709</v>
+        <v>-0.001181474480151268</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.007685098406747914</v>
+        <v>-0.001574803149606263</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.0004253308128544852</v>
+        <v>-0.002922755741127325</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.006185567010309279</v>
+        <v>-0.005144356955380558</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.004461942257217832</v>
+        <v>-0.007359081419624258</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0.003186504217432073</v>
+        <v>-0.005670103092783541</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.0111811023622047</v>
+        <v>-0.006176331918906231</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0.0003681546249425516</v>
+        <v>-0.002572178477690257</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.001096033402922747</v>
+        <v>-0.0001565762004175353</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.01227741330834116</v>
+        <v>-0.005482661668228706</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.006852551984877164</v>
+        <v>-0.004388862671071303</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.004251968503936998</v>
+        <v>-0.00141732283464564</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0.001937618147448061</v>
+        <v>-0.003202099737532782</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0.01720226843100192</v>
+        <v>-0.01060367454068238</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0.005421970768505369</v>
+        <v>-0.002296450939457184</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0.004217432052483627</v>
+        <v>-0.006091846298031878</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0.0007966260543580406</v>
+        <v>-0.0009125840537944852</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.00272965879265088</v>
+        <v>-0.003420805998125609</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0.01180880974695407</v>
+        <v>-0.005482661668228727</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0.003467666354264343</v>
+        <v>-0.002309711286089222</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.002734559170202699</v>
+        <v>-0.002099737532808343</v>
       </c>
       <c r="BQ5" t="n">
         <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0.002530459231490179</v>
+        <v>-0.004358013120899717</v>
       </c>
       <c r="BS5" t="n">
-        <v>-0.006824146981627266</v>
+        <v>-0.001546391752577347</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0.001086956521739169</v>
+        <v>-0.0009606147934678622</v>
       </c>
       <c r="BU5" t="n">
-        <v>-0.002249297094657954</v>
+        <v>-0.001574803149606263</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.02068241469816271</v>
+        <v>-0.003044619422572148</v>
       </c>
       <c r="BW5" t="n">
-        <v>-5.249343832021136e-05</v>
+        <v>-9.606147934679843e-05</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.001461377870563663</v>
+        <v>-0.0006263048016701411</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.01063730084348644</v>
+        <v>-0.01710402999062795</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.008923884514435654</v>
+        <v>-0.01640112464854736</v>
       </c>
       <c r="CA5" t="n">
-        <v>-0.002208927749654887</v>
+        <v>-0.004356955380577399</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0.001370510396975466</v>
+        <v>-0.002624179943767613</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0.01396325459317582</v>
+        <v>-0.001679790026246664</v>
       </c>
       <c r="CD5" t="n">
-        <v>-0.02708661417322834</v>
+        <v>-0.004409448818897599</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.01679790026246718</v>
+        <v>-0.004725897920604938</v>
       </c>
       <c r="CF5" t="n">
-        <v>-0.004881889763779535</v>
+        <v>-0.001510146295422388</v>
       </c>
       <c r="CG5" t="n">
-        <v>-0.003300330033003251</v>
+        <v>-0.001889763779527531</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.002170835299669682</v>
+        <v>-0.0003985828166519267</v>
       </c>
       <c r="CI5" t="n">
-        <v>-0.00103724658180101</v>
+        <v>-0.00240679565832943</v>
       </c>
       <c r="CJ5" t="n">
         <v>0</v>
       </c>
       <c r="CK5" t="n">
-        <v>0</v>
+        <v>-0.001308139534883723</v>
       </c>
       <c r="CL5" t="n">
-        <v>-0.003064592173503</v>
+        <v>-0.002828854314002838</v>
       </c>
       <c r="CM5" t="n">
-        <v>-0.001748582230623863</v>
+        <v>-0.001510146295422388</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.001275992438563367</v>
+        <v>-0.0009910335063709418</v>
       </c>
       <c r="CO5" t="n">
-        <v>-0.003307086614173194</v>
+        <v>-0.001557338367154337</v>
       </c>
       <c r="CP5" t="n">
-        <v>0</v>
+        <v>-0.0002624671916010568</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.01107611548556428</v>
+        <v>-0.002642756016989178</v>
       </c>
       <c r="CR5" t="n">
-        <v>-0.007750472589792112</v>
+        <v>-0.003544423440453737</v>
       </c>
       <c r="CS5" t="n">
-        <v>-0.008317580340264707</v>
+        <v>-0.000960614793467851</v>
       </c>
       <c r="CT5" t="n">
-        <v>-0.003300330033003251</v>
+        <v>-0.001651722510618236</v>
       </c>
       <c r="CU5" t="n">
-        <v>-8.857395925596646e-05</v>
+        <v>-0.001171508903467677</v>
       </c>
       <c r="CV5" t="n">
-        <v>-0.0003131524008350706</v>
+        <v>-0.0004360465116279077</v>
       </c>
       <c r="CW5" t="n">
         <v>0</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0.004536862003780761</v>
+        <v>-0.002404526166902421</v>
       </c>
       <c r="CY5" t="n">
-        <v>-0.004111531190926332</v>
+        <v>-0.002923149457802932</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0</v>
+        <v>-0.0007029053420806064</v>
       </c>
       <c r="DA5" t="n">
-        <v>-0.000574112734864296</v>
+        <v>-0.0001921229586935858</v>
       </c>
       <c r="DB5" t="n">
-        <v>-0.001275992438563378</v>
+        <v>-0.001982067012741884</v>
       </c>
       <c r="DC5" t="n">
-        <v>-0.002970297029702929</v>
+        <v>-0.001887682869277985</v>
       </c>
       <c r="DD5" t="n">
-        <v>-0.0005623242736645051</v>
+        <v>-0.001312335958005206</v>
       </c>
       <c r="DE5" t="n">
-        <v>-0.0006134969325153449</v>
+        <v>-0.004251968503937009</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.003166351606805351</v>
+        <v>-0.01772748703441778</v>
       </c>
       <c r="DG5" t="n">
-        <v>-0.002309711286089211</v>
+        <v>-0.002300966405890492</v>
       </c>
       <c r="DH5" t="n">
-        <v>-0.005721784776902883</v>
+        <v>-0.004196133899104238</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.004903347477604858</v>
+        <v>-0.00405469118340408</v>
       </c>
       <c r="DJ5" t="n">
-        <v>-0.008503937007874007</v>
+        <v>-0.002087682672233804</v>
       </c>
       <c r="DK5" t="n">
-        <v>-0.001651722510618236</v>
+        <v>-0.00524934383202097</v>
       </c>
       <c r="DL5" t="n">
-        <v>-4.714757190004138e-05</v>
+        <v>-0.0002609603340292255</v>
       </c>
       <c r="DM5" t="n">
-        <v>-0.0004803073967338811</v>
+        <v>-0.001978831109065837</v>
       </c>
       <c r="DN5" t="n">
-        <v>-0.009711286089238791</v>
+        <v>-0.01258840169731262</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.003254593175853005</v>
+        <v>-0.003757828810020869</v>
       </c>
       <c r="DP5" t="n">
-        <v>-0.01286089238845144</v>
+        <v>-0.002074493163602087</v>
       </c>
       <c r="DQ5" t="n">
-        <v>-0.0005198487712665623</v>
+        <v>-0.0007029053420806286</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.0008398950131233707</v>
+        <v>-0.0003748828491096923</v>
       </c>
       <c r="DS5" t="n">
-        <v>-0.001154855643044628</v>
+        <v>0</v>
       </c>
       <c r="DT5" t="n">
-        <v>-0.007244094488188957</v>
+        <v>-0.008628005657708659</v>
       </c>
       <c r="DU5" t="n">
-        <v>-0.00400754361150395</v>
+        <v>-0.01093823668081096</v>
       </c>
       <c r="DV5" t="n">
         <v>0</v>
       </c>
       <c r="DW5" t="n">
-        <v>-0.0005522319374138051</v>
+        <v>-0.001617954070981198</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.001942257217847732</v>
+        <v>-0.002887139107611514</v>
       </c>
       <c r="DY5" t="n">
-        <v>-0.008503937007873986</v>
+        <v>-0.006600660066006648</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0.0001417769376181543</v>
+        <v>-0.0001043841336116902</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.01385826771653541</v>
+        <v>-0.001008645533141273</v>
       </c>
       <c r="EB5" t="n">
-        <v>-0.004619422572178467</v>
+        <v>-0.002400835073068874</v>
       </c>
       <c r="EC5" t="n">
-        <v>-0.00351706036745405</v>
+        <v>-0.002244258872651339</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0.001196502531063115</v>
+        <v>-0.002305475504322818</v>
       </c>
       <c r="EE5" t="n">
-        <v>-0.0002359603586597481</v>
+        <v>0</v>
       </c>
       <c r="EF5" t="n">
-        <v>-0.0002828854314002482</v>
+        <v>-0.0006263048016701411</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.0005522319374137829</v>
+        <v>-0.0003775365738555969</v>
       </c>
       <c r="EH5" t="n">
-        <v>-9.372071227742307e-05</v>
+        <v>-0.001392891450528366</v>
       </c>
       <c r="EI5" t="n">
-        <v>-0.001414427157001386</v>
+        <v>-0.002834645669291302</v>
       </c>
       <c r="EJ5" t="n">
-        <v>-0.002257217847768978</v>
+        <v>-0.007191601049868735</v>
       </c>
       <c r="EK5" t="n">
-        <v>-0.0008283479061206523</v>
+        <v>-0.004094488188976375</v>
       </c>
       <c r="EL5" t="n">
-        <v>0</v>
+        <v>-0.0001565762004175353</v>
       </c>
       <c r="EM5" t="n">
-        <v>-0.0009910335063709418</v>
+        <v>-0.0003875968992248069</v>
       </c>
       <c r="EN5" t="n">
-        <v>-0.000281162136832247</v>
+        <v>-0.0001440922190201976</v>
       </c>
       <c r="EO5" t="n">
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>0</v>
+        <v>-4.719207173194962e-05</v>
       </c>
       <c r="EQ5" t="n">
-        <v>-0.004619422572178478</v>
+        <v>-0.001729106628242105</v>
       </c>
       <c r="ER5" t="n">
         <v>0</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.0001328609388839497</v>
+        <v>-9.45179584121103e-05</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0.00183727034120732</v>
+        <v>-0.002123643227937733</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0.0008966493629070426</v>
+        <v>-0.002152230971128555</v>
       </c>
       <c r="EV5" t="n">
-        <v>0</v>
+        <v>-4.686035613871153e-05</v>
       </c>
       <c r="EW5" t="n">
-        <v>-0.003359580052493416</v>
+        <v>-0.008346456692913385</v>
       </c>
       <c r="EX5" t="n">
-        <v>-0.0007029053420806175</v>
+        <v>-0.002099737532808343</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.003149606299212571</v>
+        <v>-0.002309711286089189</v>
       </c>
     </row>
     <row r="6">
@@ -3083,433 +3083,433 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.002839990186726279</v>
+        <v>-0.002319394647748183</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.0003196005486235859</v>
+        <v>-0.0002696463593312603</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0001675223970895256</v>
+        <v>-0.0001795364534247279</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0004190735399565604</v>
+        <v>-0.0002201349932315966</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0003540408992007804</v>
+        <v>-0.0003850818178825044</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.001427978341604608</v>
+        <v>-4.30002913726496e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0004286121765305628</v>
+        <v>-0.0007348954440878879</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0002180232558139594</v>
+        <v>-0.002308412716847352</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.0009282732322021508</v>
+        <v>-0.0007994186046511643</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0002126654064272482</v>
+        <v>-3.536067892504768e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.000183802376999323</v>
+        <v>-8.326672684688675e-18</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0007210313481169572</v>
+        <v>-4.813522723531305e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.002438085925510125</v>
+        <v>-0.002310475772177789</v>
       </c>
       <c r="O6" t="n">
-        <v>5.551115123125783e-18</v>
+        <v>-0.002095735408613922</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.002078050001860054</v>
+        <v>-0.0005568131796893834</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.002254147698226566</v>
+        <v>0.00017169181367305</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.001189956303386608</v>
+        <v>-0.0001054358013121093</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.002409906855875105</v>
+        <v>-0.002397817488624129</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0008329965977015269</v>
+        <v>-0.0003451449608835672</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.0004411595349812115</v>
+        <v>-0.0002844468501341152</v>
       </c>
       <c r="W6" t="n">
-        <v>0.000445837151543202</v>
+        <v>-0.001194739581139867</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.0005295154592583756</v>
+        <v>-0.0007788002065518718</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.0002306607624801976</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.000687560056777492</v>
+        <v>-0.0004358003904945479</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.0006631140003810377</v>
+        <v>-0.0006263048016701411</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.0003123895802164739</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.0008993333511932545</v>
+        <v>-0.001619671959790464</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.004067814964051061</v>
+        <v>-0.001135186434451838</v>
       </c>
       <c r="AE6" t="n">
-        <v>9.983509396596082e-05</v>
+        <v>0.0006663224106484511</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.0008476592633898965</v>
+        <v>-0.001412294146687121</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.0003026509418829259</v>
+        <v>-3.321523472102628e-05</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.0002833867642772936</v>
+        <v>-0.0001816860465116282</v>
       </c>
       <c r="AI6" t="n">
-        <v>9.996273362758438e-06</v>
+        <v>-0.0007619547472186461</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0.001486945309161927</v>
+        <v>-0.0007861691761880119</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.002667442512924709</v>
+        <v>-0.003054899040623981</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.0005473924639914167</v>
+        <v>-0.0007567488862163547</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0.003280650410985628</v>
+        <v>-0.003572798264134347</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.002383396661173145</v>
+        <v>-0.00230556641994262</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.0006997711049249345</v>
+        <v>-4.971269813547897e-05</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.0001504289906278239</v>
+        <v>-0.0007249869704561845</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.001282255265890975</v>
+        <v>-0.0005650344854814471</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.002647681925777262</v>
+        <v>0.001619267228637417</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.991099525235189e-05</v>
+        <v>-0.0009492845690842578</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0.0004015899159454384</v>
+        <v>-0.001452841492639495</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.0001648578658940358</v>
+        <v>3.937007874015852e-05</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.0003080867679791016</v>
+        <v>-0.000469408075444061</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.0006271340390522933</v>
+        <v>-0.000603217009741544</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.0002355457141682005</v>
+        <v>-0.0004740436004358306</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.0007457911336025219</v>
+        <v>-0.001364824338238124</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.00273090437927854</v>
+        <v>-0.002230611843548419</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0.001235786120794274</v>
+        <v>-0.001136050367186314</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0.002738166295756508</v>
+        <v>-0.00138697018668307</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0.0001184838180135622</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>-8.229821912642266e-05</v>
+        <v>0</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.0007374365244930209</v>
+        <v>-0.001163222056031979</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.0003889413678809045</v>
+        <v>-0.001204227677641928</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.0001539637705041536</v>
+        <v>-0.001043410585984117</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0.0003468373265569591</v>
+        <v>-0.0006608729998010765</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0.006500553051444296</v>
+        <v>-0.001350486655650274</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.0001845779174571349</v>
+        <v>-0.001368280831319177</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0.0005486966586424779</v>
+        <v>-0.001468670101349409</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0.0001090116279069769</v>
+        <v>-0.0005297155222279692</v>
       </c>
       <c r="BM6" t="n">
-        <v>-0.001249309386605949</v>
+        <v>-0.002311667358549968</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0.001085967185897516</v>
+        <v>-0.001162237215560899</v>
       </c>
       <c r="BO6" t="n">
-        <v>-0.0007130332031115294</v>
+        <v>-0.0006257388993359924</v>
       </c>
       <c r="BP6" t="n">
-        <v>-0.0007412579102171468</v>
+        <v>-0.0005156642640106678</v>
       </c>
       <c r="BQ6" t="n">
         <v>0</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0.0004349867962931686</v>
+        <v>-0.0009361106107628414</v>
       </c>
       <c r="BS6" t="n">
-        <v>-0.001249655404426683</v>
+        <v>-0.0007813372651520657</v>
       </c>
       <c r="BT6" t="n">
-        <v>1.171508903466956e-05</v>
+        <v>0</v>
       </c>
       <c r="BU6" t="n">
-        <v>-7.204610951008216e-05</v>
+        <v>-0.001173662034791403</v>
       </c>
       <c r="BV6" t="n">
-        <v>-0.0006914778322878457</v>
+        <v>-0.0005672480162867588</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0.0004150043595492648</v>
+        <v>1.178689297501034e-05</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.003732639740720189</v>
+        <v>-0.002426955771909841</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.003425886066867581</v>
+        <v>-0.001045568288178503</v>
       </c>
       <c r="CA6" t="n">
-        <v>-0.0004391175303668365</v>
+        <v>-0.000101917589811798</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0.0002920361978460406</v>
+        <v>-0.0003634192556064786</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0.0001913681653271243</v>
+        <v>-0.0004408704101954403</v>
       </c>
       <c r="CD6" t="n">
-        <v>-0.001057604650520344</v>
+        <v>-0.002153669045863815</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.00301349538488456</v>
+        <v>-0.002461167658362584</v>
       </c>
       <c r="CF6" t="n">
-        <v>-9.964570416296225e-05</v>
+        <v>-0.0009018329870652403</v>
       </c>
       <c r="CG6" t="n">
-        <v>-0.0005274779738609791</v>
+        <v>-0.001008960636400569</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.0005041573361982577</v>
+        <v>0</v>
       </c>
       <c r="CI6" t="n">
-        <v>-0.0001699709574769559</v>
+        <v>3.633720930232565e-05</v>
       </c>
       <c r="CJ6" t="n">
         <v>0</v>
       </c>
       <c r="CK6" t="n">
-        <v>5.845389846340921e-05</v>
+        <v>-0.0008100318357908753</v>
       </c>
       <c r="CL6" t="n">
-        <v>-0.0008025277726912055</v>
+        <v>-0.001137012728259365</v>
       </c>
       <c r="CM6" t="n">
-        <v>-0.001155293539551358</v>
+        <v>1.178689297501034e-05</v>
       </c>
       <c r="CN6" t="n">
-        <v>-0.0002857952437056943</v>
+        <v>1.150483202945196e-05</v>
       </c>
       <c r="CO6" t="n">
-        <v>-0.0001931908785410885</v>
+        <v>-0.0002732274219311159</v>
       </c>
       <c r="CP6" t="n">
         <v>0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0.00121918549698862</v>
+        <v>-0.0002181587214371394</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.000628540848820408</v>
+        <v>-0.0008972517049230134</v>
       </c>
       <c r="CS6" t="n">
-        <v>-0.002444270622377942</v>
+        <v>-0.0003204029483348414</v>
       </c>
       <c r="CT6" t="n">
-        <v>-0.000794953730162229</v>
+        <v>-0.0002435501025185638</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>-3.633720930232565e-05</v>
       </c>
       <c r="CV6" t="n">
-        <v>-3.514526710403365e-05</v>
+        <v>-4.78377995565632e-05</v>
       </c>
       <c r="CW6" t="n">
         <v>0</v>
       </c>
       <c r="CX6" t="n">
-        <v>-0.001778308937903678</v>
+        <v>-0.0008895763589014227</v>
       </c>
       <c r="CY6" t="n">
-        <v>-0.0006494422731465749</v>
+        <v>-0.001057409300091619</v>
       </c>
       <c r="CZ6" t="n">
         <v>0</v>
       </c>
       <c r="DA6" t="n">
-        <v>-7.824521424348863e-05</v>
+        <v>0</v>
       </c>
       <c r="DB6" t="n">
-        <v>-0.000156576200417538</v>
+        <v>-0.0005994195453332602</v>
       </c>
       <c r="DC6" t="n">
-        <v>-0.0001787196902315269</v>
+        <v>-0.0006719475732711838</v>
       </c>
       <c r="DD6" t="n">
-        <v>-7.854287254275006e-05</v>
+        <v>-0.0002466623185592903</v>
       </c>
       <c r="DE6" t="n">
-        <v>-0.0003150458619049445</v>
+        <v>-0.0005060420055392034</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.0004600618814646018</v>
+        <v>-0.001488254808658951</v>
       </c>
       <c r="DG6" t="n">
-        <v>-0.0001658311890081088</v>
+        <v>-0.0002834125441729007</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0.001086774294890705</v>
+        <v>-0.0001777999923732315</v>
       </c>
       <c r="DI6" t="n">
-        <v>-0.001200707671167578</v>
+        <v>-0.001459708589089684</v>
       </c>
       <c r="DJ6" t="n">
-        <v>-0.0003254491164602441</v>
+        <v>-0.0002332504956674281</v>
       </c>
       <c r="DK6" t="n">
-        <v>-3.602305475504108e-05</v>
+        <v>-0.001123944277078395</v>
       </c>
       <c r="DL6" t="n">
         <v>0</v>
       </c>
       <c r="DM6" t="n">
-        <v>-0.0003185131093167232</v>
+        <v>-0.001102436628313708</v>
       </c>
       <c r="DN6" t="n">
-        <v>-0.00124190764344074</v>
+        <v>-0.002473212111372652</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.0003577780366953026</v>
+        <v>-3.536067892505601e-05</v>
       </c>
       <c r="DP6" t="n">
-        <v>-0.0005857318621286856</v>
+        <v>-0.001508565293019273</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-3.602305475504108e-05</v>
+        <v>0</v>
       </c>
       <c r="DR6" t="n">
-        <v>-0.0001060820367750931</v>
+        <v>0</v>
       </c>
       <c r="DS6" t="n">
-        <v>-3.539405379896221e-05</v>
+        <v>0</v>
       </c>
       <c r="DT6" t="n">
-        <v>-0.0009463991277461475</v>
+        <v>-0.001193277147114621</v>
       </c>
       <c r="DU6" t="n">
-        <v>-0.001788201951503932</v>
+        <v>-0.003204539852527893</v>
       </c>
       <c r="DV6" t="n">
         <v>0</v>
       </c>
       <c r="DW6" t="n">
-        <v>-0.0003435922998280327</v>
+        <v>-0.0001035434882650676</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.0008505612644977679</v>
+        <v>-0.0003834429350431351</v>
       </c>
       <c r="DY6" t="n">
-        <v>-0.002464517276337649</v>
+        <v>-0.001663520528551224</v>
       </c>
       <c r="DZ6" t="n">
         <v>0</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.0001903009798064875</v>
+        <v>-0.0002180232558139539</v>
       </c>
       <c r="EB6" t="n">
-        <v>-0.001305929740754325</v>
+        <v>-0.0007008097286516108</v>
       </c>
       <c r="EC6" t="n">
-        <v>-0.0003016475688056214</v>
+        <v>-0.001082695771251638</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0.0001768033946251552</v>
+        <v>-3.633720930232565e-05</v>
       </c>
       <c r="EE6" t="n">
         <v>0</v>
       </c>
       <c r="EF6" t="n">
-        <v>-0.0001207267169416548</v>
+        <v>0</v>
       </c>
       <c r="EG6" t="n">
-        <v>-2.498001805406602e-17</v>
+        <v>-1.665334536937735e-17</v>
       </c>
       <c r="EH6" t="n">
-        <v>0</v>
+        <v>-1.942890293094024e-17</v>
       </c>
       <c r="EI6" t="n">
-        <v>-0.0004606245054422836</v>
+        <v>-0.0006268668762872715</v>
       </c>
       <c r="EJ6" t="n">
-        <v>-0.000324650999324344</v>
+        <v>-9.568408266355521e-05</v>
       </c>
       <c r="EK6" t="n">
-        <v>-0.0002831524303916977</v>
+        <v>-0.0006098759270114412</v>
       </c>
       <c r="EL6" t="n">
         <v>0</v>
       </c>
       <c r="EM6" t="n">
-        <v>-0.0001172226942871113</v>
+        <v>0</v>
       </c>
       <c r="EN6" t="n">
-        <v>-9.085256058109225e-05</v>
+        <v>0</v>
       </c>
       <c r="EO6" t="n">
         <v>0</v>
@@ -3518,7 +3518,7 @@
         <v>0</v>
       </c>
       <c r="EQ6" t="n">
-        <v>-0.0003419591554078228</v>
+        <v>-0.0003133751744929997</v>
       </c>
       <c r="ER6" t="n">
         <v>0</v>
@@ -3527,22 +3527,22 @@
         <v>0</v>
       </c>
       <c r="ET6" t="n">
-        <v>-0.0004602230605976671</v>
+        <v>-8.374616351164988e-05</v>
       </c>
       <c r="EU6" t="n">
-        <v>-0.0004879959312016513</v>
+        <v>-1.665334536937735e-17</v>
       </c>
       <c r="EV6" t="n">
         <v>0</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0.0002197200523418624</v>
+        <v>-0.0001558902369531767</v>
       </c>
       <c r="EX6" t="n">
-        <v>-6.902899217672842e-05</v>
+        <v>-0.0001415762151958489</v>
       </c>
       <c r="EY6" t="n">
-        <v>0</v>
+        <v>-0.0006223029459005158</v>
       </c>
     </row>
     <row r="7">
@@ -3552,295 +3552,295 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0004469326267837248</v>
+        <v>-0.0009024709570576938</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0002681977640306199</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>4.480418597515024e-05</v>
+        <v>0.0002927195873771605</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0001909653179925641</v>
+        <v>0.0001178689297501034</v>
       </c>
       <c r="F7" t="n">
-        <v>-7.26744186046513e-05</v>
+        <v>4.658345000892461e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0002360041128528223</v>
+        <v>0.0002890641891116596</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2.357378595002069e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0003226031257081652</v>
+        <v>-0.001098621826881929</v>
       </c>
       <c r="J7" t="n">
-        <v>-7.358195012210355e-05</v>
+        <v>0.0002757339507201029</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001565762004175353</v>
+        <v>9.851276643801921e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001833918676746371</v>
+        <v>0.0001048361908832396</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0002161383285302521</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0004052732228425893</v>
+        <v>-0.0005854092057358262</v>
       </c>
       <c r="O7" t="n">
-        <v>0.000137318938251052</v>
+        <v>-0.0007667899581716875</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.0007710925408878633</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.001790996308358717</v>
+        <v>0.0008158495616257533</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.0004471606846879528</v>
+        <v>0.0005519623806234219</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0003658023773085662</v>
+        <v>0.0002417705428676586</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0001412444996025886</v>
+        <v>4.758915578671474e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0002964471443980598</v>
+        <v>0.0002745605200512757</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0001929607041529891</v>
+        <v>-7.433555661984226e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001318959631557526</v>
+        <v>0.0002785462529921401</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0004309519054005228</v>
+        <v>0.0004353313787640756</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>-7.288385496950212e-05</v>
+        <v>0.0002593116454502442</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0005031946959624167</v>
+        <v>0.0004566059477263851</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.397645910771079e-05</v>
+        <v>4.428697962798323e-05</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.0003357963049840373</v>
+        <v>-0.001160935136161995</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.00111625736308264</v>
+        <v>0.001441806327149209</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.006825309491672671</v>
+        <v>0.008438302889950461</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.0002370626111602658</v>
+        <v>-0.0002960718262741635</v>
       </c>
       <c r="AG7" t="n">
-        <v>-7.02905342080673e-05</v>
+        <v>0.0001211240310077522</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0.0001526236568285877</v>
+        <v>0.0001225750798367453</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.0002154191748078627</v>
+        <v>-0.0002820237841162865</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0.0007983493489260528</v>
+        <v>-0.0002559269141035547</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.003703687214510215</v>
+        <v>0.005836164200823413</v>
       </c>
       <c r="AL7" t="n">
-        <v>9.570859160913936e-05</v>
+        <v>-0.0003027253654722506</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0.0004425196585717827</v>
+        <v>0.001402943813059121</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.0001363256358636045</v>
+        <v>-0.0001294442186186684</v>
       </c>
       <c r="AO7" t="n">
-        <v>-7.550104478813442e-05</v>
+        <v>0.0008205695331218454</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.0004032448441860958</v>
+        <v>-0.0002556293887106542</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.0002412279836300546</v>
+        <v>0.0007510925605922646</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.0061629126473767</v>
+        <v>0.003797492931650098</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.0002111490390927562</v>
+        <v>-0.000526588711376541</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.0001610676484123164</v>
+        <v>-9.857748317113058e-05</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.0004430708132654448</v>
+        <v>0.0004501325265397815</v>
       </c>
       <c r="AV7" t="n">
-        <v>9.203865623562124e-05</v>
+        <v>0.0001328609388839497</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.0003052494646176851</v>
+        <v>-4.428697962799988e-05</v>
       </c>
       <c r="AX7" t="n">
+        <v>-2.401536983669961e-05</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>-0.0004940642071334933</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>-0.0001158642020914313</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0.0001787682967800019</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0.0001171508903467344</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>6.987002019760437e-05</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0.0001550044286979468</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>-0.0007217499052653897</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0.0005992631299811757</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>-0.0001534898310735167</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>0.0001218324244854685</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>-0.0005234206708577104</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>-0.0001676882548861669</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>-0.0002874425731609786</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>-0.0008014786669108265</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>0.0005044802608060561</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>-0.000163413135640611</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>-9.689922480620173e-05</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>4.725897920602739e-05</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>4.725897920602185e-05</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>0.0001373189382510298</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>-0.0002148794041360757</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>0.0002961906331321373</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>-6.643046944199149e-05</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>0.0003789565196464672</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>2.602678139226322e-05</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>-0.0001683161027397018</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>-9.429514380011605e-05</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>-0.0009557927372975173</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>-0.000470632715795688</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>-1.110223024625157e-17</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>-0.0002150466728213396</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>0.0004956622451334769</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>0.0003540524184743321</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>-0.0006901557157033833</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>-0.0006429239761756467</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>0.0002903412538445949</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>0.0003538853075153392</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>-0.000209189546582389</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>2.357378595002069e-05</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>-0.0003267484465532544</v>
+      </c>
+      <c r="CS7" t="n">
         <v>-4.844961240310086e-05</v>
       </c>
-      <c r="AY7" t="n">
-        <v>-0.0002617103354288608</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0.0002233067781626741</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>-0.0004263419465339758</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>-0.0003204154393336933</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>-0.0003003532659072494</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>0.0003548660980247142</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>0.000760105155359836</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>-9.48179084186429e-05</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>-0.0007479509180830291</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>0.0008004312820029836</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>-7.072135785005096e-05</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>4.615885965069122e-05</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>-0.0001654398809582347</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>2.660148918109395e-05</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>-0.0004249962754839576</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>-7.078810759792443e-05</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>0.000152833746014791</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>-0.0004263667612504129</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>0.0003065704669300728</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>0.0004773064185914111</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>4.577297941700809e-05</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>0.0002382818183442659</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>-0.0002193155542303204</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>0.000137980159625456</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>0.0002139304090969185</v>
-      </c>
-      <c r="CB7" t="n">
-        <v>-4.844961240310086e-05</v>
-      </c>
-      <c r="CC7" t="n">
-        <v>9.455000126050716e-05</v>
-      </c>
-      <c r="CD7" t="n">
-        <v>-0.0002379457789335626</v>
-      </c>
-      <c r="CE7" t="n">
-        <v>-0.0003173527649054653</v>
-      </c>
-      <c r="CF7" t="n">
-        <v>0.0001181474480151046</v>
-      </c>
-      <c r="CG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH7" t="n">
-        <v>4.891390744674596e-05</v>
-      </c>
-      <c r="CI7" t="n">
-        <v>0.0002376376945426306</v>
-      </c>
-      <c r="CJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK7" t="n">
-        <v>0.0004978856571298373</v>
-      </c>
-      <c r="CL7" t="n">
-        <v>-7.204610951009882e-05</v>
-      </c>
-      <c r="CM7" t="n">
-        <v>-2.422480620155043e-05</v>
-      </c>
-      <c r="CN7" t="n">
-        <v>4.719207173194962e-05</v>
-      </c>
-      <c r="CO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ7" t="n">
-        <v>-4.714757190001917e-05</v>
-      </c>
-      <c r="CR7" t="n">
-        <v>-0.0002602289190543783</v>
-      </c>
-      <c r="CS7" t="n">
-        <v>-0.0008759092249101929</v>
-      </c>
       <c r="CT7" t="n">
-        <v>-0.0004112945437480752</v>
+        <v>0.0003115806291154766</v>
       </c>
       <c r="CU7" t="n">
         <v>0</v>
@@ -3852,10 +3852,10 @@
         <v>0</v>
       </c>
       <c r="CX7" t="n">
-        <v>-5.177449971876524e-05</v>
+        <v>-0.00029444448319072</v>
       </c>
       <c r="CY7" t="n">
-        <v>9.606147934679842e-05</v>
+        <v>-0.0001574803149606452</v>
       </c>
       <c r="CZ7" t="n">
         <v>0</v>
@@ -3864,49 +3864,49 @@
         <v>0</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.000117980179329874</v>
+        <v>0</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.0001196575152127566</v>
+        <v>-0.0002064428890061198</v>
       </c>
       <c r="DD7" t="n">
         <v>0</v>
       </c>
       <c r="DE7" t="n">
-        <v>0</v>
+        <v>-0.0001415762151958489</v>
       </c>
       <c r="DF7" t="n">
-        <v>-2.242329225185524e-05</v>
+        <v>-0.0001800530106159326</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.0003603590567382908</v>
+        <v>9.689922480620173e-05</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.0002359381087438106</v>
+        <v>-4.686035613871708e-05</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.0002633304002622072</v>
+        <v>-4.719207173194962e-05</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0</v>
+        <v>-9.648035207650009e-05</v>
       </c>
       <c r="DK7" t="n">
-        <v>2.357378595002624e-05</v>
+        <v>-0.0001826722338204578</v>
       </c>
       <c r="DL7" t="n">
-        <v>2.214348981399716e-05</v>
+        <v>0</v>
       </c>
       <c r="DM7" t="n">
-        <v>-2.220446049250313e-17</v>
+        <v>-0.0005970295741516529</v>
       </c>
       <c r="DN7" t="n">
-        <v>9.45179584120881e-05</v>
+        <v>-0.000376950202048526</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.0001816059178790463</v>
+        <v>4.725897920604405e-05</v>
       </c>
       <c r="DP7" t="n">
-        <v>-0.0001650165016501448</v>
+        <v>0.0002258928975070018</v>
       </c>
       <c r="DQ7" t="n">
         <v>0</v>
@@ -3915,61 +3915,61 @@
         <v>0</v>
       </c>
       <c r="DS7" t="n">
-        <v>0</v>
+        <v>2.359603586597481e-05</v>
       </c>
       <c r="DT7" t="n">
-        <v>-0.0003349571758015591</v>
+        <v>-0.0002386761624243672</v>
       </c>
       <c r="DU7" t="n">
-        <v>-0.0009751342855398803</v>
+        <v>-0.001515690972454958</v>
       </c>
       <c r="DV7" t="n">
         <v>0</v>
       </c>
       <c r="DW7" t="n">
-        <v>-0.0001049868766404227</v>
+        <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>-5.551115123125783e-18</v>
+        <v>0</v>
       </c>
       <c r="DY7" t="n">
-        <v>-0.0005420830801338927</v>
+        <v>0.0005996065734676759</v>
       </c>
       <c r="DZ7" t="n">
         <v>0</v>
       </c>
       <c r="EA7" t="n">
-        <v>-4.601932811781895e-05</v>
+        <v>0.0001752726024207507</v>
       </c>
       <c r="EB7" t="n">
-        <v>-0.000260142766332816</v>
+        <v>-0.0002137975614609267</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.0004355863043562002</v>
+        <v>4.530576072522274e-05</v>
       </c>
       <c r="ED7" t="n">
-        <v>2.609603340292255e-05</v>
+        <v>0.0001178143215332495</v>
       </c>
       <c r="EE7" t="n">
         <v>0</v>
       </c>
       <c r="EF7" t="n">
-        <v>2.359603586597481e-05</v>
+        <v>2.343017806934466e-05</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.0001388049380400824</v>
+        <v>4.658345000892461e-05</v>
       </c>
       <c r="EH7" t="n">
         <v>0</v>
       </c>
       <c r="EI7" t="n">
-        <v>-0.0001004315900227592</v>
+        <v>-2.401536983669961e-05</v>
       </c>
       <c r="EJ7" t="n">
-        <v>-9.418959932407377e-05</v>
+        <v>2.214348981398606e-05</v>
       </c>
       <c r="EK7" t="n">
-        <v>0</v>
+        <v>-0.0001878400476221953</v>
       </c>
       <c r="EL7" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
         <v>0</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.0002044381613473867</v>
+        <v>-0.0001677876936152955</v>
       </c>
       <c r="ER7" t="n">
         <v>0</v>
@@ -3996,22 +3996,22 @@
         <v>0</v>
       </c>
       <c r="ET7" t="n">
-        <v>-0.0001854731840621682</v>
+        <v>0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0.0001150483202945474</v>
+        <v>0.000251903653504143</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
       </c>
       <c r="EW7" t="n">
-        <v>-4.803073967338811e-05</v>
+        <v>0.0001171508903467455</v>
       </c>
       <c r="EX7" t="n">
         <v>0</v>
       </c>
       <c r="EY7" t="n">
-        <v>4.601932811780785e-05</v>
+        <v>-9.45179584121103e-05</v>
       </c>
     </row>
     <row r="8">
@@ -4021,433 +4021,433 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001481156176200823</v>
+        <v>-7.902526553948131e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0007204209146272427</v>
+        <v>0.0003838737586851326</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0004125151538310057</v>
+        <v>0.0007027169746102762</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.539405379896221e-05</v>
+        <v>0.0004096210092518426</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0001780838585233257</v>
+        <v>0.0003809427357316181</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0005472415717563712</v>
+        <v>0.0008064200754453494</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0002307164661331296</v>
+        <v>0.0005225730239771408</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001099266829357945</v>
+        <v>-0.0003007824700409251</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0004422729304232764</v>
+        <v>0.0007407524339854088</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0004341406134565573</v>
+        <v>0.0004811689421827942</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0002870267973393181</v>
+        <v>0.0003519144235769683</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0005529220823806886</v>
+        <v>0.0006299584716371765</v>
       </c>
       <c r="N8" t="n">
-        <v>0.001197508236840794</v>
+        <v>0.0007386930799035574</v>
       </c>
       <c r="O8" t="n">
-        <v>0.000426851528703856</v>
+        <v>0.0003141888460347131</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0002717495586768176</v>
+        <v>0.0007227830409870545</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.004605208928649926</v>
+        <v>0.002007531802329527</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0008159495483828576</v>
+        <v>0.001015268308172138</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0007547505336985699</v>
+        <v>0.001646169731579539</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0003357459420421094</v>
+        <v>8.401182838911058e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0003720287961039264</v>
+        <v>0.0005384588184573796</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0004337189201395391</v>
+        <v>0.0008434864104966993</v>
       </c>
       <c r="W8" t="n">
-        <v>0.001550673442204484</v>
+        <v>0.0008293211960699986</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0017981286176283</v>
+        <v>0.001700074756953757</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.643046944200813e-05</v>
+        <v>0.0001935007913131337</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.001098227559922951</v>
+        <v>0.002283352349047579</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.0007737040221673958</v>
+        <v>0.001003149334805894</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0003697360960881913</v>
+        <v>0.0003693697670851093</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.0009040639722015242</v>
+        <v>-2.422480620157541e-05</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.007276321316580825</v>
+        <v>0.006327844122324735</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.009436801071353454</v>
+        <v>0.01283561317595226</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.0008252531222739639</v>
+        <v>3.536067892503104e-05</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.0002132442267777063</v>
+        <v>0.0003469040763047715</v>
       </c>
       <c r="AH8" t="n">
-        <v>9.62704544706261e-05</v>
+        <v>0.0002947168242071668</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.001073846251968719</v>
+        <v>0.0007940436587224764</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.0003700828970896353</v>
+        <v>0.002289619410948324</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.0119846091188648</v>
+        <v>0.00963845020317641</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.0002423850476903716</v>
+        <v>4.543295631073696e-05</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.002710455621830535</v>
+        <v>0.004142246303897468</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.0005549866355795713</v>
+        <v>0.0003139552219172087</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.000545452178108191</v>
+        <v>0.002244903564243575</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.0007699856364374064</v>
+        <v>-1.181474480151656e-05</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.0001689448730752774</v>
+        <v>0.001306507478644395</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.01447174688102939</v>
+        <v>0.007116471519398921</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.000986010574326654</v>
+        <v>0.0003420868952667522</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.0008628855046772215</v>
+        <v>0.001212582801162637</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.0009091433792044578</v>
+        <v>0.0007737040221673652</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.0004826594174910769</v>
+        <v>0.0006122003952972243</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.0003418281348888469</v>
+        <v>0.0005514064307644533</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.0001023139434303433</v>
+        <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.000523947750969006</v>
+        <v>0.0007248044178554736</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.0007913093834363089</v>
+        <v>0.000754372275358714</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.0002916408299219686</v>
+        <v>0.001200135365835764</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.000304758172698194</v>
+        <v>0.0003992044240511722</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>0.0002171302809161585</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.643242383204626e-05</v>
+        <v>0.000336366088359008</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.001133954790304714</v>
+        <v>0.0009373595340275181</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.001028943563994231</v>
+        <v>0.0004845159441679819</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.001715035532314818</v>
+        <v>0.001058125967333024</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.0003412005614239544</v>
+        <v>0</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.003036862196456905</v>
+        <v>0.002945349282334384</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.00106008010710433</v>
+        <v>0.0005031054843633698</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.0008646851154228668</v>
+        <v>0.001006240470684527</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.0001680236567782295</v>
+        <v>-0.000122482601013929</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.0001896499595550161</v>
+        <v>0.0001862427480834955</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.0003403765048461988</v>
+        <v>0.001267404398895655</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.0001939948387162743</v>
+        <v>9.668978844134534e-05</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.0002458806411482023</v>
+        <v>0.0001035434882650676</v>
       </c>
       <c r="BQ8" t="n">
         <v>0</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.0006263432853751334</v>
+        <v>0.0006993755281670844</v>
       </c>
       <c r="BS8" t="n">
-        <v>0</v>
+        <v>0.0005995200955043801</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.000690196885265365</v>
+        <v>0.0003492731195919863</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.001018971155625048</v>
+        <v>-4.725897920606071e-05</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.0001330269977436738</v>
+        <v>0.001542601157894283</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.0006914778322878762</v>
+        <v>0.00108015580760932</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.0006124161396220517</v>
+        <v>0.001485315389221084</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.0006408054643343847</v>
+        <v>0.001862484839463488</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.00049924541959733</v>
+        <v>0.000641628256054394</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.0003628334638186542</v>
+        <v>-8.326672684688674e-18</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.0004186438138038013</v>
+        <v>0.0002123643227937733</v>
       </c>
       <c r="CD8" t="n">
-        <v>-3.633720930235063e-05</v>
+        <v>0.0003776173546373163</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.0004155892720854287</v>
+        <v>-3.321523472099575e-05</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.000434140613456524</v>
+        <v>0.0007156124128834846</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.0009318913943856145</v>
+        <v>-0.0001350063830880377</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.0004158655313434706</v>
+        <v>0.0007054970164220076</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.001288610110005539</v>
+        <v>0.0004558368046519684</v>
       </c>
       <c r="CJ8" t="n">
         <v>0</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.001222342633905499</v>
+        <v>0.0009333369874929525</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.0002850800956376853</v>
+        <v>-0.0002008751449673441</v>
       </c>
       <c r="CM8" t="n">
-        <v>3.32152347210124e-05</v>
+        <v>0.0006300917238098196</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.0001422268626279727</v>
+        <v>0.0005298164124524275</v>
       </c>
       <c r="CO8" t="n">
-        <v>0</v>
+        <v>0.0002229464271037152</v>
       </c>
       <c r="CP8" t="n">
-        <v>4.558624099535447e-05</v>
+        <v>0.0002123664391267016</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.0003638012829689036</v>
+        <v>0.0004597665099735082</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.0001184330516412424</v>
+        <v>0.000558351203696858</v>
       </c>
       <c r="CS8" t="n">
-        <v>-0.0004628481833438891</v>
+        <v>0.0001535544706250031</v>
       </c>
       <c r="CT8" t="n">
-        <v>7.029053420805342e-05</v>
+        <v>0.0008779936888796414</v>
       </c>
       <c r="CU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>7.874015748031703e-05</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>0.0004242484936949203</v>
+      </c>
+      <c r="CY8" t="n">
+        <v>0.000547230815601582</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>0.000860024944941759</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>0.0006444295526740057</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>0.0001848680480440845</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>0.0003149606299212626</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>0.0006646629659147307</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>0.0005203561144571572</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>0.001015569774095851</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>7.088846880904943e-05</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>3.321523472097077e-05</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>-0.0001312498637780407</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>0.0001772211720226652</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>0.0005620044209533187</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>0.000829077773432027</v>
+      </c>
+      <c r="DQ8" t="n">
+        <v>0.0001063327032136074</v>
+      </c>
+      <c r="DR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS8" t="n">
+        <v>0.0002229840057249438</v>
+      </c>
+      <c r="DT8" t="n">
+        <v>0.0004896675338080609</v>
+      </c>
+      <c r="DU8" t="n">
+        <v>-0.0001288659793814484</v>
+      </c>
+      <c r="DV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY8" t="n">
+        <v>0.001532827495424646</v>
+      </c>
+      <c r="DZ8" t="n">
+        <v>0.0002188020655648104</v>
+      </c>
+      <c r="EA8" t="n">
+        <v>0.0005536249501238461</v>
+      </c>
+      <c r="EB8" t="n">
+        <v>0.0002660214414051898</v>
+      </c>
+      <c r="EC8" t="n">
+        <v>0.0005604319606174385</v>
+      </c>
+      <c r="ED8" t="n">
+        <v>0.0003012947700682833</v>
+      </c>
+      <c r="EE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF8" t="n">
+        <v>0.0002997454583098663</v>
+      </c>
+      <c r="EG8" t="n">
+        <v>0.0002279184023259717</v>
+      </c>
+      <c r="EH8" t="n">
+        <v>0.0001414427157001241</v>
+      </c>
+      <c r="EI8" t="n">
+        <v>0.0003223455538298725</v>
+      </c>
+      <c r="EJ8" t="n">
+        <v>0.0004101717240943325</v>
+      </c>
+      <c r="EK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM8" t="n">
         <v>7.029053420805066e-05</v>
       </c>
-      <c r="CV8" t="n">
-        <v>7.078810759792443e-05</v>
-      </c>
-      <c r="CW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX8" t="n">
-        <v>0.0004266149565942734</v>
-      </c>
-      <c r="CY8" t="n">
-        <v>0.0009379969661178129</v>
-      </c>
-      <c r="CZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA8" t="n">
-        <v>0.0001416840221705018</v>
-      </c>
-      <c r="DB8" t="n">
-        <v>0.000611232800988859</v>
-      </c>
-      <c r="DC8" t="n">
-        <v>0.0003088948910456108</v>
-      </c>
-      <c r="DD8" t="n">
-        <v>7.072135785010371e-05</v>
-      </c>
-      <c r="DE8" t="n">
-        <v>0.0001957202505219191</v>
-      </c>
-      <c r="DF8" t="n">
-        <v>0.0004970150205902135</v>
-      </c>
-      <c r="DG8" t="n">
-        <v>0.0006243827325669055</v>
-      </c>
-      <c r="DH8" t="n">
-        <v>0.0005821641764406721</v>
-      </c>
-      <c r="DI8" t="n">
-        <v>0.0009057273362010092</v>
-      </c>
-      <c r="DJ8" t="n">
-        <v>0.0004601226993865087</v>
-      </c>
-      <c r="DK8" t="n">
-        <v>9.117248199070059e-05</v>
-      </c>
-      <c r="DL8" t="n">
-        <v>4.665009913347729e-05</v>
-      </c>
-      <c r="DM8" t="n">
-        <v>5.148248184095039e-05</v>
-      </c>
-      <c r="DN8" t="n">
-        <v>0.0006732067602096491</v>
-      </c>
-      <c r="DO8" t="n">
-        <v>0.0002709100272158871</v>
-      </c>
-      <c r="DP8" t="n">
-        <v>0.0003227428678959782</v>
-      </c>
-      <c r="DQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT8" t="n">
-        <v>0.0007820951162279017</v>
-      </c>
-      <c r="DU8" t="n">
-        <v>1.239356515201629e-05</v>
-      </c>
-      <c r="DV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX8" t="n">
-        <v>1.665334536937735e-17</v>
-      </c>
-      <c r="DY8" t="n">
-        <v>0.0002827283332014541</v>
-      </c>
-      <c r="DZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="EA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="EB8" t="n">
-        <v>0.0001978698253341293</v>
-      </c>
-      <c r="EC8" t="n">
-        <v>0.0008827245021998525</v>
-      </c>
-      <c r="ED8" t="n">
-        <v>0.0005746133007786591</v>
-      </c>
-      <c r="EE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="EF8" t="n">
-        <v>0.0003927828165519676</v>
-      </c>
-      <c r="EG8" t="n">
-        <v>0.000525362782893815</v>
-      </c>
-      <c r="EH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="EI8" t="n">
-        <v>7.204610951008216e-05</v>
-      </c>
-      <c r="EJ8" t="n">
-        <v>0.000430584551148222</v>
-      </c>
-      <c r="EK8" t="n">
-        <v>0.0001768033946251968</v>
-      </c>
-      <c r="EL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="EM8" t="n">
-        <v>0</v>
-      </c>
       <c r="EN8" t="n">
-        <v>3.536067892503936e-05</v>
+        <v>0</v>
       </c>
       <c r="EO8" t="n">
         <v>0</v>
@@ -4456,7 +4456,7 @@
         <v>0</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.0004967600785911825</v>
+        <v>0.0001367587229860551</v>
       </c>
       <c r="ER8" t="n">
         <v>0</v>
@@ -4465,22 +4465,22 @@
         <v>0</v>
       </c>
       <c r="ET8" t="n">
-        <v>-1.200768491834703e-05</v>
+        <v>0.0003865979381442952</v>
       </c>
       <c r="EU8" t="n">
-        <v>3.514526710402533e-05</v>
+        <v>0.0004834791572794539</v>
       </c>
       <c r="EV8" t="n">
         <v>0</v>
       </c>
       <c r="EW8" t="n">
-        <v>8.300087190982464e-05</v>
+        <v>0.0008938917388781275</v>
       </c>
       <c r="EX8" t="n">
         <v>0</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.0001528763847176789</v>
+        <v>3.633720930232565e-05</v>
       </c>
     </row>
     <row r="9">
@@ -4490,466 +4490,466 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>0.001252609603340282</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.0005774278215223249</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.001565762004175353</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.001018600531443747</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.001312335958005284</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.002788279773156843</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.00193487494100989</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.0005062126092958863</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.002312411514865454</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.000702905342080562</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0007550731477111938</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.003373945641986864</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.005377906976744107</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0008506616257088595</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.002729658792650935</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.01569767441860457</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.002123643227937688</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.005406824146981648</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.0009203865623561569</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.001284322409211724</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.002501179801793252</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.001370510396975377</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.002922940655447281</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.0008283479061205412</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.003045923149015917</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.001682905225863596</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.0009372071227740974</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.0005283381364072692</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.01065616797900265</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.02722868217054257</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.005154639175257691</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.00160680529300562</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.001380579843534235</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.002265219443133515</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.01342155009451794</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.03488372093023251</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.001320132013201281</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.009932170542635566</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0.001564657156005478</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.003119092627599196</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0.0006299212598425364</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0.002485043718361712</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0.01981589147286814</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0.001505757307351641</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0.008333333333333238</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.00964147286821696</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0.0007306889352818313</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0.00222868217054264</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0.0003149606299212682</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0.001647286821705429</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0.003175333640128853</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0.001564657156005489</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0.003549060542797466</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0.0004175365344467608</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0.0008034026465028044</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0.003464566929133883</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0.002192066805845494</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0.003166351606805251</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0.0008857395925597866</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>0.01148255813953479</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0.002162908421537035</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0.002470930232558122</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0.0008414526129317812</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0.000849457291175093</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>0.007170542635658817</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>0.004489603024574629</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0.001030927835051498</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0.00276115968706857</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>0.001426599171652043</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>0.001356993736951972</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>0.0006200177147918318</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0.002389878163074033</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>0.001978831109065771</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>0.002116889093419216</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>0.005135658914728602</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>0.002519379844961222</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>0.001252609603340282</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0.001417769376181421</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>0.001218369259606344</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>0.0004247286455875465</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>0.001207349081364861</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0.000598251265531502</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>0.001564657156005489</v>
+      </c>
+      <c r="CI9" t="n">
         <v>0.002887139107611558</v>
       </c>
-      <c r="C9" t="n">
-        <v>0.001218369259606333</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.001043841336116902</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.0003985828166519489</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.0002828854314003149</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.005564304461942293</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.00229615745079661</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.003517060367454083</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.004279749478079309</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.0009372071227740752</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.00165016501650167</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.002208927749654799</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.007349081364829413</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.002519685039370101</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0.001518637827887659</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.006764841233317953</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.003183716075156551</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.01086614173228346</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0.0007204610951008772</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0.002400835073068874</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0.005721784776902905</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0.002362204724409489</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0.006106471816283954</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0.0003308128544423306</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0.001827553889409528</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0.005774278215223127</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0.001469816272965907</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0.007620041753653484</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0.01480314960629925</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0.01691762621789198</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0.003092783505154617</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0.001356993736951972</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0.001058444546709558</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0.004251968503937009</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0.00586011342155005</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0.01837270341207351</v>
-      </c>
-      <c r="AL9" t="n">
+      <c r="CJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>0.001948627103631528</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>0.002577082374597339</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>0.0008979206049149035</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>0.001312089971883756</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>0.0007971656333037869</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>0.0004428697962798323</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>0.001200417536534437</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>0.002296157450796599</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>0.0007550731477111938</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>0.002717900656044969</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>0.0003775365738555969</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>0.0004175365344467608</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>0.001886792452830155</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>0.001968134957825651</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>0.00128854118729862</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>0.001334560515416439</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>0.001102362204724439</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>4.844961240310086e-05</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>0.001012425218591773</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>0.002715140358950763</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>0.001508722300801468</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>0.005091863517060391</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>0.00232558139534883</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>0.001225836869401198</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>0.001650165016501626</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>0.0002835538752362643</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>0.00174446016030172</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>0.001211240310077522</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>0.002257217847769066</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>0.001986434108527135</v>
+      </c>
+      <c r="DQ9" t="n">
+        <v>0.0003149606299212682</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>9.20386562356157e-05</v>
+      </c>
+      <c r="DS9" t="n">
+        <v>0.0007828810020876764</v>
+      </c>
+      <c r="DT9" t="n">
+        <v>0.002024850437183601</v>
+      </c>
+      <c r="DU9" t="n">
+        <v>0.001275992438563289</v>
+      </c>
+      <c r="DV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>4.719207173194962e-05</v>
+      </c>
+      <c r="DX9" t="n">
+        <v>0.0002214348981399161</v>
+      </c>
+      <c r="DY9" t="n">
+        <v>0.006734496124030908</v>
+      </c>
+      <c r="DZ9" t="n">
+        <v>0.001994750656168032</v>
+      </c>
+      <c r="EA9" t="n">
+        <v>0.001012425218591773</v>
+      </c>
+      <c r="EB9" t="n">
+        <v>0.0004360465116279077</v>
+      </c>
+      <c r="EC9" t="n">
+        <v>0.000895803866100875</v>
+      </c>
+      <c r="ED9" t="n">
+        <v>0.001039697542533069</v>
+      </c>
+      <c r="EE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF9" t="n">
+        <v>0.0007349081364829591</v>
+      </c>
+      <c r="EG9" t="n">
+        <v>0.001837270341207398</v>
+      </c>
+      <c r="EH9" t="n">
+        <v>0.001627296587926552</v>
+      </c>
+      <c r="EI9" t="n">
+        <v>0.0007072135785006761</v>
+      </c>
+      <c r="EJ9" t="n">
         <v>0.0008872651356993666</v>
       </c>
-      <c r="AM9" t="n">
-        <v>0.008716075156576242</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>0.001681075888568684</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0.007769028871391093</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0.001627296587926541</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0.001150483202945196</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0.02074669187145555</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0.001426599171652043</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0.001732283464566953</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0.004776902887139112</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0.003359580052493461</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0.003653444676409157</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0.0009394572025052117</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>0.003254593175853038</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0.004294478527607393</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>0.001826722338204578</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>0.007306889352818413</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>0.001784776902887175</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>0.0004719207173194961</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>0.004577630957999091</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>0.004853862212943616</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>0.002483598875351422</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>0.004199475065616798</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>0.009394572025052228</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>0.004018789144050072</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>0.008818897637795298</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>0.0004714757190005136</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>0.000339147286821706</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>0.001550387596899228</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>0.005301837270341225</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>0.0004724409448819133</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>0.01049868766404203</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>0.000874367234238338</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>0.002087682672233804</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>0.002729658792650957</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>0.0005154639175257381</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>4.714757190005248e-05</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>0.0009438414346389923</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>0.00111434108527132</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>0.001196502531063004</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>0.001461377870563663</v>
-      </c>
-      <c r="CB9" t="n">
-        <v>0.0009394572025052117</v>
-      </c>
-      <c r="CC9" t="n">
-        <v>0.0007306889352818313</v>
-      </c>
-      <c r="CD9" t="n">
-        <v>0.0006200177147918984</v>
-      </c>
-      <c r="CE9" t="n">
-        <v>0.001774530271398733</v>
-      </c>
-      <c r="CF9" t="n">
-        <v>0.001043841336116902</v>
-      </c>
-      <c r="CG9" t="n">
-        <v>0.004881889763779556</v>
-      </c>
-      <c r="CH9" t="n">
-        <v>0.0006616257088846611</v>
-      </c>
-      <c r="CI9" t="n">
-        <v>0.002887139107611581</v>
-      </c>
-      <c r="CJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK9" t="n">
-        <v>0.002029259084473834</v>
-      </c>
-      <c r="CL9" t="n">
-        <v>0.0006902899217671177</v>
-      </c>
-      <c r="CM9" t="n">
-        <v>0.0007306889352818313</v>
-      </c>
-      <c r="CN9" t="n">
-        <v>0.0002300966405890392</v>
-      </c>
-      <c r="CO9" t="n">
-        <v>5.219206680584509e-05</v>
-      </c>
-      <c r="CP9" t="n">
-        <v>0.0003780718336483635</v>
-      </c>
-      <c r="CQ9" t="n">
-        <v>0.001030927835051521</v>
-      </c>
-      <c r="CR9" t="n">
-        <v>0.002123643227937733</v>
-      </c>
-      <c r="CS9" t="n">
-        <v>0.0001840773124711981</v>
-      </c>
-      <c r="CT9" t="n">
-        <v>0.006246719160105019</v>
-      </c>
-      <c r="CU9" t="n">
-        <v>0.0004697286012526058</v>
-      </c>
-      <c r="CV9" t="n">
-        <v>0.0003674540682414795</v>
-      </c>
-      <c r="CW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX9" t="n">
-        <v>0.001784776902887186</v>
-      </c>
-      <c r="CY9" t="n">
-        <v>0.002782152230971169</v>
-      </c>
-      <c r="CZ9" t="n">
-        <v>0.0004724409448819022</v>
-      </c>
-      <c r="DA9" t="n">
-        <v>0.0007497656982192735</v>
-      </c>
-      <c r="DB9" t="n">
-        <v>0.001889763779527598</v>
-      </c>
-      <c r="DC9" t="n">
-        <v>0.001656695812241082</v>
-      </c>
-      <c r="DD9" t="n">
-        <v>0.001102362204724439</v>
-      </c>
-      <c r="DE9" t="n">
-        <v>0.0008414526129318589</v>
-      </c>
-      <c r="DF9" t="n">
-        <v>0.002362204724409489</v>
-      </c>
-      <c r="DG9" t="n">
-        <v>0.001417769376181421</v>
-      </c>
-      <c r="DH9" t="n">
-        <v>0.001017441860465118</v>
-      </c>
-      <c r="DI9" t="n">
-        <v>0.002348643006263029</v>
-      </c>
-      <c r="DJ9" t="n">
-        <v>0.002453027139874719</v>
-      </c>
-      <c r="DK9" t="n">
-        <v>0.000519848771266529</v>
-      </c>
-      <c r="DL9" t="n">
-        <v>0.0005219206680584509</v>
-      </c>
-      <c r="DM9" t="n">
-        <v>0.0006263048016701411</v>
-      </c>
-      <c r="DN9" t="n">
-        <v>0.002061855670103074</v>
-      </c>
-      <c r="DO9" t="n">
-        <v>0.002422480620155043</v>
-      </c>
-      <c r="DP9" t="n">
-        <v>0.001984877126653994</v>
-      </c>
-      <c r="DQ9" t="n">
-        <v>0.0005249343832021136</v>
-      </c>
-      <c r="DR9" t="n">
-        <v>4.686035613870043e-05</v>
-      </c>
-      <c r="DS9" t="n">
-        <v>0.0003653444676409157</v>
-      </c>
-      <c r="DT9" t="n">
-        <v>0.001795841209829807</v>
-      </c>
-      <c r="DU9" t="n">
-        <v>0.0004141739530602706</v>
-      </c>
-      <c r="DV9" t="n">
-        <v>0</v>
-      </c>
-      <c r="DW9" t="n">
-        <v>0.0003542958370239546</v>
-      </c>
-      <c r="DX9" t="n">
-        <v>0.0003653444676409157</v>
-      </c>
-      <c r="DY9" t="n">
-        <v>0.001065891472868219</v>
-      </c>
-      <c r="DZ9" t="n">
-        <v>0.0003149606299212682</v>
-      </c>
-      <c r="EA9" t="n">
-        <v>0.001565762004175353</v>
-      </c>
-      <c r="EB9" t="n">
-        <v>0.001039697542533058</v>
-      </c>
-      <c r="EC9" t="n">
-        <v>0.001453488372093026</v>
-      </c>
-      <c r="ED9" t="n">
-        <v>0.001843100189035862</v>
-      </c>
-      <c r="EE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="EF9" t="n">
-        <v>0.001984877126654017</v>
-      </c>
-      <c r="EG9" t="n">
-        <v>0.003412073490813661</v>
-      </c>
-      <c r="EH9" t="n">
-        <v>0.0003131524008350706</v>
-      </c>
-      <c r="EI9" t="n">
-        <v>0.002992125984251981</v>
-      </c>
-      <c r="EJ9" t="n">
-        <v>0.0008966493629070426</v>
-      </c>
       <c r="EK9" t="n">
-        <v>0.0007828810020876764</v>
+        <v>0.0003300330033002896</v>
       </c>
       <c r="EL9" t="n">
-        <v>0</v>
+        <v>0.0008506616257088817</v>
       </c>
       <c r="EM9" t="n">
-        <v>0.0001921229586935746</v>
+        <v>0.0009973753280840159</v>
       </c>
       <c r="EN9" t="n">
-        <v>0.0001565762004175353</v>
+        <v>4.686035613868933e-05</v>
       </c>
       <c r="EO9" t="n">
         <v>0</v>
       </c>
       <c r="EP9" t="n">
-        <v>4.601932811780785e-05</v>
+        <v>0.0001043841336116902</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.0008165225744476534</v>
+        <v>0.0004714757190004249</v>
       </c>
       <c r="ER9" t="n">
-        <v>5.249343832021136e-05</v>
+        <v>0.0002609603340292255</v>
       </c>
       <c r="ES9" t="n">
-        <v>0</v>
+        <v>0.0001874414245548017</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.0004697286012526058</v>
+        <v>0.0008350730688935215</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.001086956521739091</v>
+        <v>0.000849457291175093</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.0001405810684161013</v>
+        <v>0.0002087682672233804</v>
       </c>
       <c r="EW9" t="n">
-        <v>0.0006784968684759862</v>
+        <v>0.001555869872701532</v>
       </c>
       <c r="EX9" t="n">
-        <v>0.000849457291175093</v>
+        <v>0.0004686035613870376</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.0005191127890514458</v>
+        <v>0.0001328609388839497</v>
       </c>
     </row>
   </sheetData>
